--- a/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -110,15 +110,15 @@
     <t>main.o</t>
   </si>
   <si>
+    <t>oled_app.o</t>
+  </si>
+  <si>
     <t>dadd.o</t>
   </si>
   <si>
     <t>gd32f4xx_gpio.o</t>
   </si>
   <si>
-    <t>oled_app.o</t>
-  </si>
-  <si>
     <t>diskio.o</t>
   </si>
   <si>
@@ -179,6 +179,9 @@
     <t>cpp_init.o</t>
   </si>
   <si>
+    <t>adc_app.o</t>
+  </si>
+  <si>
     <t>f2d.o</t>
   </si>
   <si>
@@ -204,9 +207,6 @@
   </si>
   <si>
     <t>memcmp.o</t>
-  </si>
-  <si>
-    <t>adc_app.o</t>
   </si>
   <si>
     <t>strlen.o</t>
@@ -405,52 +405,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="69"/>
                 <c:pt idx="0">
-                  <c:v>73.33273315429688</c:v>
+                  <c:v>73.31961059570313</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.29970455169678</c:v>
+                  <c:v>12.2975025177002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.388953685760498</c:v>
+                  <c:v>5.40588903427124</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.610151290893555</c:v>
+                  <c:v>4.609325885772705</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.75454306602478</c:v>
+                  <c:v>1.754228949546814</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6534777283668518</c:v>
+                  <c:v>0.6533607840538025</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5460567474365234</c:v>
+                  <c:v>0.5459589958190918</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.5371050238609314</c:v>
+                  <c:v>0.5370088815689087</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3222630023956299</c:v>
+                  <c:v>0.3222053050994873</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2058902531862259</c:v>
+                  <c:v>0.2058534026145935</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1432279944419861</c:v>
+                  <c:v>0.1432023644447327</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.06266225129365921</c:v>
+                  <c:v>0.06265103071928024</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05371050164103508</c:v>
+                  <c:v>0.05370088666677475</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.03580699861049652</c:v>
+                  <c:v>0.03580059111118317</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.03580699861049652</c:v>
+                  <c:v>0.03580059111118317</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01790349930524826</c:v>
+                  <c:v>0.01790029555559158</c:v>
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0</c:v>
@@ -599,16 +599,16 @@
                   <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>oled_app.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>gd32f4xx_pmu.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>gd32f4xx_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>oled_app.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>diskio.o</c:v>
@@ -683,34 +683,34 @@
                   <c:v>cpp_init.o</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>adc_app.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>systick_wrapper_ual.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>memcmp.o</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>adc_app.o</c:v>
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>strlen.o</c:v>
@@ -740,208 +740,208 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="69"/>
                 <c:pt idx="0">
-                  <c:v>15.00209331512451</c:v>
+                  <c:v>14.97372055053711</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.13371658325195</c:v>
+                  <c:v>13.10887813568115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.061779975891113</c:v>
+                  <c:v>8.04653263092041</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.561350345611572</c:v>
+                  <c:v>6.548941135406494</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.160354137420654</c:v>
+                  <c:v>6.148703575134277</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.369379043579102</c:v>
+                  <c:v>5.359224319458008</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.067530155181885</c:v>
+                  <c:v>5.057946681976318</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.697093963623047</c:v>
+                  <c:v>3.690101861953735</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.46134352684021</c:v>
+                  <c:v>3.454797267913818</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.943574190139771</c:v>
+                  <c:v>2.938007116317749</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.432414531707764</c:v>
+                  <c:v>2.427814245223999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.780245423316956</c:v>
+                  <c:v>1.776878595352173</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.55110490322113</c:v>
+                  <c:v>1.548171401023865</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.533478736877441</c:v>
+                  <c:v>1.53057861328125</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.405688881874085</c:v>
+                  <c:v>1.403030395507813</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.379249572753906</c:v>
+                  <c:v>1.376641035079956</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.247053146362305</c:v>
+                  <c:v>1.244694709777832</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.207394242286682</c:v>
+                  <c:v>1.205110669136047</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.189767956733704</c:v>
+                  <c:v>1.187517881393433</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.145702481269836</c:v>
+                  <c:v>1.143535733222961</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.061978101730347</c:v>
+                  <c:v>1.059969663619995</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.022319197654724</c:v>
+                  <c:v>1.0203857421875</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9782536625862122</c:v>
+                  <c:v>0.9764035940170288</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.9606274962425232</c:v>
+                  <c:v>0.9588107466697693</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.9363914728164673</c:v>
+                  <c:v>0.9346205592155457</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7358935475349426</c:v>
+                  <c:v>0.7432982325553894</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6565756797790527</c:v>
+                  <c:v>0.7345017790794373</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.62132328748703</c:v>
+                  <c:v>0.655333936214447</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5948839783668518</c:v>
+                  <c:v>0.620148241519928</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5199726819992065</c:v>
+                  <c:v>0.5189892649650574</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5023465156555176</c:v>
+                  <c:v>0.5013964176177979</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.497939944267273</c:v>
+                  <c:v>0.4969982206821442</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4891268312931061</c:v>
+                  <c:v>0.4882017970085144</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4759072065353394</c:v>
+                  <c:v>0.4750071465969086</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.458281010389328</c:v>
+                  <c:v>0.4574142992496491</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4098089635372162</c:v>
+                  <c:v>0.4090339243412018</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4098089635372162</c:v>
+                  <c:v>0.4090339243412018</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3745566010475159</c:v>
+                  <c:v>0.3738482296466827</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3745566010475159</c:v>
+                  <c:v>0.3738482296466827</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3723533153533936</c:v>
+                  <c:v>0.3716491162776947</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3613369464874268</c:v>
+                  <c:v>0.3606535792350769</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2908321619033814</c:v>
+                  <c:v>0.2902821600437164</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2599863409996033</c:v>
+                  <c:v>0.2594946324825287</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2467667013406754</c:v>
+                  <c:v>0.2462999969720841</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2159208655357361</c:v>
+                  <c:v>0.2155124992132187</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2159208655357361</c:v>
+                  <c:v>0.2155124992132187</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.1894815713167191</c:v>
+                  <c:v>0.1891232132911682</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1410095393657684</c:v>
+                  <c:v>0.1407428532838821</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1057571545243263</c:v>
+                  <c:v>0.1055571436882019</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1057571545243263</c:v>
+                  <c:v>0.1055571436882019</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1057571545243263</c:v>
+                  <c:v>0.1055571436882019</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.09694405645132065</c:v>
+                  <c:v>0.09676071256399155</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.08813096582889557</c:v>
+                  <c:v>0.08796428889036179</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.08372441679239273</c:v>
+                  <c:v>0.08796428889036179</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.07931786775588989</c:v>
+                  <c:v>0.08356606960296631</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.07931786775588989</c:v>
+                  <c:v>0.07916785776615143</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.07931786775588989</c:v>
+                  <c:v>0.07916785776615143</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.07931786775588989</c:v>
+                  <c:v>0.07916785776615143</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.07050476968288422</c:v>
+                  <c:v>0.07916785776615143</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.06609822064638138</c:v>
+                  <c:v>0.07037142664194107</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.06609822064638138</c:v>
+                  <c:v>0.06597321480512619</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.057285126298666</c:v>
+                  <c:v>0.06597321480512619</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.04847202822566032</c:v>
+                  <c:v>0.05717678740620613</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.03084583766758442</c:v>
+                  <c:v>0.03078749962151051</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.01762619242072105</c:v>
+                  <c:v>0.01759285666048527</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.01762619242072105</c:v>
+                  <c:v>0.01759285666048527</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.008813096210360527</c:v>
+                  <c:v>0.008796428330242634</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.008813096210360527</c:v>
+                  <c:v>0.008796428330242634</c:v>
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0</c:v>
@@ -1408,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>73.33273315429688</v>
+        <v>73.31961059570313</v>
       </c>
       <c r="C3" s="1">
         <v>8192</v>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>12.29970455169678</v>
+        <v>12.2975025177002</v>
       </c>
       <c r="C4" s="1">
         <v>1374</v>
@@ -1460,10 +1460,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>5.388953685760498</v>
+        <v>5.40588903427124</v>
       </c>
       <c r="C5" s="1">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D5" s="1">
         <v>2796</v>
@@ -1478,7 +1478,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1486,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>4.610151290893555</v>
+        <v>4.609325885772705</v>
       </c>
       <c r="C6" s="1">
         <v>515</v>
@@ -1512,7 +1512,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.75454306602478</v>
+        <v>1.754228949546814</v>
       </c>
       <c r="C7" s="1">
         <v>196</v>
@@ -1538,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.6534777283668518</v>
+        <v>0.6533607840538025</v>
       </c>
       <c r="C8" s="1">
         <v>73</v>
@@ -1564,7 +1564,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.5460567474365234</v>
+        <v>0.5459589958190918</v>
       </c>
       <c r="C9" s="1">
         <v>61</v>
@@ -1590,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.5371050238609314</v>
+        <v>0.5370088815689087</v>
       </c>
       <c r="C10" s="1">
         <v>60</v>
@@ -1616,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3222630023956299</v>
+        <v>0.3222053050994873</v>
       </c>
       <c r="C11" s="1">
         <v>36</v>
@@ -1642,7 +1642,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2058902531862259</v>
+        <v>0.2058534026145935</v>
       </c>
       <c r="C12" s="1">
         <v>23</v>
@@ -1668,7 +1668,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1432279944419861</v>
+        <v>0.1432023644447327</v>
       </c>
       <c r="C13" s="1">
         <v>16</v>
@@ -1694,7 +1694,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.06266225129365921</v>
+        <v>0.06265103071928024</v>
       </c>
       <c r="C14" s="1">
         <v>7</v>
@@ -1720,7 +1720,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05371050164103508</v>
+        <v>0.05370088666677475</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.03580699861049652</v>
+        <v>0.03580059111118317</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
@@ -1772,7 +1772,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.03580699861049652</v>
+        <v>0.03580059111118317</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -1798,7 +1798,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01790349930524826</v>
+        <v>0.01790029555559158</v>
       </c>
       <c r="C18" s="1">
         <v>2</v>
@@ -1905,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>15.00209331512451</v>
+        <v>14.97372055053711</v>
       </c>
       <c r="C3" s="1">
         <v>6809</v>
@@ -1931,7 +1931,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>13.13371658325195</v>
+        <v>13.10887813568115</v>
       </c>
       <c r="C4" s="1">
         <v>5961</v>
@@ -1957,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>8.061779975891113</v>
+        <v>8.04653263092041</v>
       </c>
       <c r="C5" s="1">
         <v>3659</v>
@@ -1983,7 +1983,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>6.561350345611572</v>
+        <v>6.548941135406494</v>
       </c>
       <c r="C6" s="1">
         <v>2978</v>
@@ -2009,13 +2009,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>6.160354137420654</v>
+        <v>6.148703575134277</v>
       </c>
       <c r="C7" s="1">
         <v>2796</v>
       </c>
       <c r="D7" s="1">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E7" s="1">
         <v>2794</v>
@@ -2027,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2035,7 +2035,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="2">
-        <v>5.369379043579102</v>
+        <v>5.359224319458008</v>
       </c>
       <c r="C8" s="1">
         <v>2437</v>
@@ -2061,7 +2061,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>5.067530155181885</v>
+        <v>5.057946681976318</v>
       </c>
       <c r="C9" s="1">
         <v>2300</v>
@@ -2087,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>3.697093963623047</v>
+        <v>3.690101861953735</v>
       </c>
       <c r="C10" s="1">
         <v>1678</v>
@@ -2113,7 +2113,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>3.46134352684021</v>
+        <v>3.454797267913818</v>
       </c>
       <c r="C11" s="1">
         <v>1571</v>
@@ -2139,7 +2139,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>2.943574190139771</v>
+        <v>2.938007116317749</v>
       </c>
       <c r="C12" s="1">
         <v>1336</v>
@@ -2165,7 +2165,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>2.432414531707764</v>
+        <v>2.427814245223999</v>
       </c>
       <c r="C13" s="1">
         <v>1104</v>
@@ -2191,7 +2191,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>1.780245423316956</v>
+        <v>1.776878595352173</v>
       </c>
       <c r="C14" s="1">
         <v>808</v>
@@ -2217,7 +2217,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>1.55110490322113</v>
+        <v>1.548171401023865</v>
       </c>
       <c r="C15" s="1">
         <v>704</v>
@@ -2243,7 +2243,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2">
-        <v>1.533478736877441</v>
+        <v>1.53057861328125</v>
       </c>
       <c r="C16" s="1">
         <v>696</v>
@@ -2269,7 +2269,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>1.405688881874085</v>
+        <v>1.403030395507813</v>
       </c>
       <c r="C17" s="1">
         <v>638</v>
@@ -2295,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="2">
-        <v>1.379249572753906</v>
+        <v>1.376641035079956</v>
       </c>
       <c r="C18" s="1">
         <v>626</v>
@@ -2321,7 +2321,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2">
-        <v>1.247053146362305</v>
+        <v>1.244694709777832</v>
       </c>
       <c r="C19" s="1">
         <v>566</v>
@@ -2347,7 +2347,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="2">
-        <v>1.207394242286682</v>
+        <v>1.205110669136047</v>
       </c>
       <c r="C20" s="1">
         <v>548</v>
@@ -2373,7 +2373,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="2">
-        <v>1.189767956733704</v>
+        <v>1.187517881393433</v>
       </c>
       <c r="C21" s="1">
         <v>540</v>
@@ -2399,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2">
-        <v>1.145702481269836</v>
+        <v>1.143535733222961</v>
       </c>
       <c r="C22" s="1">
         <v>520</v>
@@ -2425,7 +2425,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="2">
-        <v>1.061978101730347</v>
+        <v>1.059969663619995</v>
       </c>
       <c r="C23" s="1">
         <v>482</v>
@@ -2451,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>1.022319197654724</v>
+        <v>1.0203857421875</v>
       </c>
       <c r="C24" s="1">
         <v>464</v>
@@ -2477,7 +2477,7 @@
         <v>28</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9782536625862122</v>
+        <v>0.9764035940170288</v>
       </c>
       <c r="C25" s="1">
         <v>444</v>
@@ -2503,7 +2503,7 @@
         <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>0.9606274962425232</v>
+        <v>0.9588107466697693</v>
       </c>
       <c r="C26" s="1">
         <v>436</v>
@@ -2529,7 +2529,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="2">
-        <v>0.9363914728164673</v>
+        <v>0.9346205592155457</v>
       </c>
       <c r="C27" s="1">
         <v>425</v>
@@ -2555,16 +2555,16 @@
         <v>31</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7358935475349426</v>
+        <v>0.7432982325553894</v>
       </c>
       <c r="C28" s="1">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2578,19 +2578,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6565756797790527</v>
+        <v>0.7345017790794373</v>
       </c>
       <c r="C29" s="1">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="D29" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2599,24 +2599,24 @@
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B30" s="2">
-        <v>0.62132328748703</v>
+        <v>0.655333936214447</v>
       </c>
       <c r="C30" s="1">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E30" s="1">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2633,16 +2633,16 @@
         <v>33</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5948839783668518</v>
+        <v>0.620148241519928</v>
       </c>
       <c r="C31" s="1">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5199726819992065</v>
+        <v>0.5189892649650574</v>
       </c>
       <c r="C32" s="1">
         <v>236</v>
@@ -2685,7 +2685,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5023465156555176</v>
+        <v>0.5013964176177979</v>
       </c>
       <c r="C33" s="1">
         <v>228</v>
@@ -2711,7 +2711,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>0.497939944267273</v>
+        <v>0.4969982206821442</v>
       </c>
       <c r="C34" s="1">
         <v>226</v>
@@ -2737,7 +2737,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4891268312931061</v>
+        <v>0.4882017970085144</v>
       </c>
       <c r="C35" s="1">
         <v>222</v>
@@ -2763,7 +2763,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4759072065353394</v>
+        <v>0.4750071465969086</v>
       </c>
       <c r="C36" s="1">
         <v>216</v>
@@ -2789,7 +2789,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="2">
-        <v>0.458281010389328</v>
+        <v>0.4574142992496491</v>
       </c>
       <c r="C37" s="1">
         <v>208</v>
@@ -2815,7 +2815,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4098089635372162</v>
+        <v>0.4090339243412018</v>
       </c>
       <c r="C38" s="1">
         <v>186</v>
@@ -2841,7 +2841,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="2">
-        <v>0.4098089635372162</v>
+        <v>0.4090339243412018</v>
       </c>
       <c r="C39" s="1">
         <v>186</v>
@@ -2867,7 +2867,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3745566010475159</v>
+        <v>0.3738482296466827</v>
       </c>
       <c r="C40" s="1">
         <v>170</v>
@@ -2893,7 +2893,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3745566010475159</v>
+        <v>0.3738482296466827</v>
       </c>
       <c r="C41" s="1">
         <v>170</v>
@@ -2919,7 +2919,7 @@
         <v>12</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3723533153533936</v>
+        <v>0.3716491162776947</v>
       </c>
       <c r="C42" s="1">
         <v>169</v>
@@ -2945,7 +2945,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3613369464874268</v>
+        <v>0.3606535792350769</v>
       </c>
       <c r="C43" s="1">
         <v>164</v>
@@ -2971,7 +2971,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2908321619033814</v>
+        <v>0.2902821600437164</v>
       </c>
       <c r="C44" s="1">
         <v>132</v>
@@ -2997,7 +2997,7 @@
         <v>14</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2599863409996033</v>
+        <v>0.2594946324825287</v>
       </c>
       <c r="C45" s="1">
         <v>118</v>
@@ -3023,7 +3023,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2467667013406754</v>
+        <v>0.2462999969720841</v>
       </c>
       <c r="C46" s="1">
         <v>112</v>
@@ -3049,7 +3049,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2159208655357361</v>
+        <v>0.2155124992132187</v>
       </c>
       <c r="C47" s="1">
         <v>98</v>
@@ -3075,7 +3075,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2159208655357361</v>
+        <v>0.2155124992132187</v>
       </c>
       <c r="C48" s="1">
         <v>98</v>
@@ -3101,7 +3101,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.1894815713167191</v>
+        <v>0.1891232132911682</v>
       </c>
       <c r="C49" s="1">
         <v>86</v>
@@ -3127,7 +3127,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.1410095393657684</v>
+        <v>0.1407428532838821</v>
       </c>
       <c r="C50" s="1">
         <v>64</v>
@@ -3153,7 +3153,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1057571545243263</v>
+        <v>0.1055571436882019</v>
       </c>
       <c r="C51" s="1">
         <v>48</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1057571545243263</v>
+        <v>0.1055571436882019</v>
       </c>
       <c r="C52" s="1">
         <v>48</v>
@@ -3205,7 +3205,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1057571545243263</v>
+        <v>0.1055571436882019</v>
       </c>
       <c r="C53" s="1">
         <v>48</v>
@@ -3231,7 +3231,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.09694405645132065</v>
+        <v>0.09676071256399155</v>
       </c>
       <c r="C54" s="1">
         <v>44</v>
@@ -3257,7 +3257,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.08813096582889557</v>
+        <v>0.08796428889036179</v>
       </c>
       <c r="C55" s="1">
         <v>40</v>
@@ -3283,16 +3283,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.08372441679239273</v>
+        <v>0.08796428889036179</v>
       </c>
       <c r="C56" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3309,16 +3309,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.07931786775588989</v>
+        <v>0.08356606960296631</v>
       </c>
       <c r="C57" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.07931786775588989</v>
+        <v>0.07916785776615143</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3361,7 +3361,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.07931786775588989</v>
+        <v>0.07916785776615143</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3387,7 +3387,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.07931786775588989</v>
+        <v>0.07916785776615143</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3413,16 +3413,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.07050476968288422</v>
+        <v>0.07916785776615143</v>
       </c>
       <c r="C61" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3439,16 +3439,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.06609822064638138</v>
+        <v>0.07037142664194107</v>
       </c>
       <c r="C62" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.06609822064638138</v>
+        <v>0.06597321480512619</v>
       </c>
       <c r="C63" s="1">
         <v>30</v>
@@ -3491,16 +3491,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.057285126298666</v>
+        <v>0.06597321480512619</v>
       </c>
       <c r="C64" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3517,16 +3517,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.04847202822566032</v>
+        <v>0.05717678740620613</v>
       </c>
       <c r="C65" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3543,7 +3543,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.03084583766758442</v>
+        <v>0.03078749962151051</v>
       </c>
       <c r="C66" s="1">
         <v>14</v>
@@ -3569,7 +3569,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.01762619242072105</v>
+        <v>0.01759285666048527</v>
       </c>
       <c r="C67" s="1">
         <v>8</v>
@@ -3595,7 +3595,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.01762619242072105</v>
+        <v>0.01759285666048527</v>
       </c>
       <c r="C68" s="1">
         <v>8</v>
@@ -3621,7 +3621,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.008813096210360527</v>
+        <v>0.008796428330242634</v>
       </c>
       <c r="C69" s="1">
         <v>4</v>
@@ -3647,7 +3647,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.008813096210360527</v>
+        <v>0.008796428330242634</v>
       </c>
       <c r="C70" s="1">
         <v>4</v>

--- a/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -572,16 +572,16 @@
                   <c:v>gd32f4xx_sdio.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>btn_app.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>gd32f4xx_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>gd32f4xx_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>gd32f4xx_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>btn_app.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>gd30ad3344.o</c:v>
@@ -740,208 +740,208 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="69"/>
                 <c:pt idx="0">
-                  <c:v>14.97372055053711</c:v>
+                  <c:v>14.95070552825928</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.10887813568115</c:v>
+                  <c:v>13.08872890472412</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.04653263092041</c:v>
+                  <c:v>8.034165382385254</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.548941135406494</c:v>
+                  <c:v>6.538875579833984</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.148703575134277</c:v>
+                  <c:v>6.13925313949585</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.359224319458008</c:v>
+                  <c:v>5.350986957550049</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.057946681976318</c:v>
+                  <c:v>5.050172328948975</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.690101861953735</c:v>
+                  <c:v>3.684430122375488</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.454797267913818</c:v>
+                  <c:v>3.449487209320068</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.938007116317749</c:v>
+                  <c:v>2.933491468429565</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.427814245223999</c:v>
+                  <c:v>2.424082756042481</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.776878595352173</c:v>
+                  <c:v>1.774147510528565</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.548171401023865</c:v>
+                  <c:v>1.545791864395142</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.53057861328125</c:v>
+                  <c:v>1.528226017951965</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.403030395507813</c:v>
+                  <c:v>1.400873899459839</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.376641035079956</c:v>
+                  <c:v>1.374525189399719</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.244694709777832</c:v>
+                  <c:v>1.295478940010071</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.205110669136047</c:v>
+                  <c:v>1.242781519889832</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.187517881393433</c:v>
+                  <c:v>1.203258514404297</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.143535733222961</c:v>
+                  <c:v>1.185692667961121</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.059969663619995</c:v>
+                  <c:v>1.058340430259705</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.0203857421875</c:v>
+                  <c:v>1.01881742477417</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9764035940170288</c:v>
+                  <c:v>0.974902868270874</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.9588107466697693</c:v>
+                  <c:v>0.9573370218276978</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.9346205592155457</c:v>
+                  <c:v>0.933184027671814</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7432982325553894</c:v>
+                  <c:v>0.7421557903289795</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.7345017790794373</c:v>
+                  <c:v>0.7333728671073914</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.655333936214447</c:v>
+                  <c:v>0.6543266773223877</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.620148241519928</c:v>
+                  <c:v>0.6191950440406799</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5189892649650574</c:v>
+                  <c:v>0.5181915760040283</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5013964176177979</c:v>
+                  <c:v>0.5006257891654968</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4969982206821442</c:v>
+                  <c:v>0.4962343275547028</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4882017970085144</c:v>
+                  <c:v>0.487451434135437</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4750071465969086</c:v>
+                  <c:v>0.4742770493030548</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4574142992496491</c:v>
+                  <c:v>0.4567112326622009</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4090339243412018</c:v>
+                  <c:v>0.4084052443504334</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4090339243412018</c:v>
+                  <c:v>0.4084052443504334</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3738482296466827</c:v>
+                  <c:v>0.3732736110687256</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3738482296466827</c:v>
+                  <c:v>0.3732736110687256</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3716491162776947</c:v>
+                  <c:v>0.3710778951644898</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3606535792350769</c:v>
+                  <c:v>0.3600992560386658</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2902821600437164</c:v>
+                  <c:v>0.2898359894752502</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2594946324825287</c:v>
+                  <c:v>0.2590957880020142</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2462999969720841</c:v>
+                  <c:v>0.2459214329719544</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2155124992132187</c:v>
+                  <c:v>0.2151812613010407</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2155124992132187</c:v>
+                  <c:v>0.2151812613010407</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.1891232132911682</c:v>
+                  <c:v>0.1888325363397598</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1407428532838821</c:v>
+                  <c:v>0.1405265331268311</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1055571436882019</c:v>
+                  <c:v>0.1053948998451233</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1055571436882019</c:v>
+                  <c:v>0.1053948998451233</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1055571436882019</c:v>
+                  <c:v>0.1053948998451233</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.09676071256399155</c:v>
+                  <c:v>0.09661199152469635</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.08796428889036179</c:v>
+                  <c:v>0.08782908320426941</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.08796428889036179</c:v>
+                  <c:v>0.08782908320426941</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.08356606960296631</c:v>
+                  <c:v>0.08343762904405594</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.07916785776615143</c:v>
+                  <c:v>0.07904617488384247</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.07916785776615143</c:v>
+                  <c:v>0.07904617488384247</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.07916785776615143</c:v>
+                  <c:v>0.07904617488384247</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.07916785776615143</c:v>
+                  <c:v>0.07904617488384247</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.07037142664194107</c:v>
+                  <c:v>0.07026326656341553</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.06597321480512619</c:v>
+                  <c:v>0.06587181240320206</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.06597321480512619</c:v>
+                  <c:v>0.06587181240320206</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.05717678740620613</c:v>
+                  <c:v>0.05708890408277512</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.03078749962151051</c:v>
+                  <c:v>0.03074017912149429</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.01759285666048527</c:v>
+                  <c:v>0.01756581664085388</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.01759285666048527</c:v>
+                  <c:v>0.01756581664085388</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.008796428330242634</c:v>
+                  <c:v>0.008782908320426941</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.008796428330242634</c:v>
+                  <c:v>0.008782908320426941</c:v>
                 </c:pt>
                 <c:pt idx="68">
                   <c:v>0</c:v>
@@ -1518,10 +1518,10 @@
         <v>196</v>
       </c>
       <c r="D7" s="1">
-        <v>520</v>
+        <v>590</v>
       </c>
       <c r="E7" s="1">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="F7" s="1">
         <v>14</v>
@@ -1905,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>14.97372055053711</v>
+        <v>14.95070552825928</v>
       </c>
       <c r="C3" s="1">
         <v>6809</v>
@@ -1931,7 +1931,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>13.10887813568115</v>
+        <v>13.08872890472412</v>
       </c>
       <c r="C4" s="1">
         <v>5961</v>
@@ -1957,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>8.04653263092041</v>
+        <v>8.034165382385254</v>
       </c>
       <c r="C5" s="1">
         <v>3659</v>
@@ -1983,7 +1983,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2">
-        <v>6.548941135406494</v>
+        <v>6.538875579833984</v>
       </c>
       <c r="C6" s="1">
         <v>2978</v>
@@ -2009,7 +2009,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>6.148703575134277</v>
+        <v>6.13925313949585</v>
       </c>
       <c r="C7" s="1">
         <v>2796</v>
@@ -2035,7 +2035,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="2">
-        <v>5.359224319458008</v>
+        <v>5.350986957550049</v>
       </c>
       <c r="C8" s="1">
         <v>2437</v>
@@ -2061,7 +2061,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="2">
-        <v>5.057946681976318</v>
+        <v>5.050172328948975</v>
       </c>
       <c r="C9" s="1">
         <v>2300</v>
@@ -2087,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>3.690101861953735</v>
+        <v>3.684430122375488</v>
       </c>
       <c r="C10" s="1">
         <v>1678</v>
@@ -2113,7 +2113,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>3.454797267913818</v>
+        <v>3.449487209320068</v>
       </c>
       <c r="C11" s="1">
         <v>1571</v>
@@ -2139,7 +2139,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>2.938007116317749</v>
+        <v>2.933491468429565</v>
       </c>
       <c r="C12" s="1">
         <v>1336</v>
@@ -2165,7 +2165,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>2.427814245223999</v>
+        <v>2.424082756042481</v>
       </c>
       <c r="C13" s="1">
         <v>1104</v>
@@ -2191,7 +2191,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>1.776878595352173</v>
+        <v>1.774147510528565</v>
       </c>
       <c r="C14" s="1">
         <v>808</v>
@@ -2217,7 +2217,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>1.548171401023865</v>
+        <v>1.545791864395142</v>
       </c>
       <c r="C15" s="1">
         <v>704</v>
@@ -2243,7 +2243,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2">
-        <v>1.53057861328125</v>
+        <v>1.528226017951965</v>
       </c>
       <c r="C16" s="1">
         <v>696</v>
@@ -2269,7 +2269,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="2">
-        <v>1.403030395507813</v>
+        <v>1.400873899459839</v>
       </c>
       <c r="C17" s="1">
         <v>638</v>
@@ -2295,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="2">
-        <v>1.376641035079956</v>
+        <v>1.374525189399719</v>
       </c>
       <c r="C18" s="1">
         <v>626</v>
@@ -2318,25 +2318,25 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2">
-        <v>1.244694709777832</v>
+        <v>1.295478940010071</v>
       </c>
       <c r="C19" s="1">
-        <v>566</v>
+        <v>590</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="E19" s="1">
-        <v>566</v>
+        <v>380</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -2344,19 +2344,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2">
-        <v>1.205110669136047</v>
+        <v>1.242781519889832</v>
       </c>
       <c r="C20" s="1">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2370,19 +2370,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2">
-        <v>1.187517881393433</v>
+        <v>1.203258514404297</v>
       </c>
       <c r="C21" s="1">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2396,25 +2396,25 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2">
-        <v>1.143535733222961</v>
+        <v>1.185692667961121</v>
       </c>
       <c r="C22" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="D22" s="1">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>310</v>
+        <v>540</v>
       </c>
       <c r="F22" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="2">
-        <v>1.059969663619995</v>
+        <v>1.058340430259705</v>
       </c>
       <c r="C23" s="1">
         <v>482</v>
@@ -2451,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>1.0203857421875</v>
+        <v>1.01881742477417</v>
       </c>
       <c r="C24" s="1">
         <v>464</v>
@@ -2477,7 +2477,7 @@
         <v>28</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9764035940170288</v>
+        <v>0.974902868270874</v>
       </c>
       <c r="C25" s="1">
         <v>444</v>
@@ -2503,7 +2503,7 @@
         <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>0.9588107466697693</v>
+        <v>0.9573370218276978</v>
       </c>
       <c r="C26" s="1">
         <v>436</v>
@@ -2529,7 +2529,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="2">
-        <v>0.9346205592155457</v>
+        <v>0.933184027671814</v>
       </c>
       <c r="C27" s="1">
         <v>425</v>
@@ -2555,7 +2555,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7432982325553894</v>
+        <v>0.7421557903289795</v>
       </c>
       <c r="C28" s="1">
         <v>338</v>
@@ -2581,7 +2581,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="2">
-        <v>0.7345017790794373</v>
+        <v>0.7333728671073914</v>
       </c>
       <c r="C29" s="1">
         <v>334</v>
@@ -2607,7 +2607,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="2">
-        <v>0.655333936214447</v>
+        <v>0.6543266773223877</v>
       </c>
       <c r="C30" s="1">
         <v>298</v>
@@ -2633,7 +2633,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="2">
-        <v>0.620148241519928</v>
+        <v>0.6191950440406799</v>
       </c>
       <c r="C31" s="1">
         <v>282</v>
@@ -2659,7 +2659,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5189892649650574</v>
+        <v>0.5181915760040283</v>
       </c>
       <c r="C32" s="1">
         <v>236</v>
@@ -2685,7 +2685,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5013964176177979</v>
+        <v>0.5006257891654968</v>
       </c>
       <c r="C33" s="1">
         <v>228</v>
@@ -2711,7 +2711,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4969982206821442</v>
+        <v>0.4962343275547028</v>
       </c>
       <c r="C34" s="1">
         <v>226</v>
@@ -2737,7 +2737,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4882017970085144</v>
+        <v>0.487451434135437</v>
       </c>
       <c r="C35" s="1">
         <v>222</v>
@@ -2763,7 +2763,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4750071465969086</v>
+        <v>0.4742770493030548</v>
       </c>
       <c r="C36" s="1">
         <v>216</v>
@@ -2789,7 +2789,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4574142992496491</v>
+        <v>0.4567112326622009</v>
       </c>
       <c r="C37" s="1">
         <v>208</v>
@@ -2815,7 +2815,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4090339243412018</v>
+        <v>0.4084052443504334</v>
       </c>
       <c r="C38" s="1">
         <v>186</v>
@@ -2841,7 +2841,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="2">
-        <v>0.4090339243412018</v>
+        <v>0.4084052443504334</v>
       </c>
       <c r="C39" s="1">
         <v>186</v>
@@ -2867,7 +2867,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3738482296466827</v>
+        <v>0.3732736110687256</v>
       </c>
       <c r="C40" s="1">
         <v>170</v>
@@ -2893,7 +2893,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3738482296466827</v>
+        <v>0.3732736110687256</v>
       </c>
       <c r="C41" s="1">
         <v>170</v>
@@ -2919,7 +2919,7 @@
         <v>12</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3716491162776947</v>
+        <v>0.3710778951644898</v>
       </c>
       <c r="C42" s="1">
         <v>169</v>
@@ -2945,7 +2945,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3606535792350769</v>
+        <v>0.3600992560386658</v>
       </c>
       <c r="C43" s="1">
         <v>164</v>
@@ -2971,7 +2971,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2902821600437164</v>
+        <v>0.2898359894752502</v>
       </c>
       <c r="C44" s="1">
         <v>132</v>
@@ -2997,7 +2997,7 @@
         <v>14</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2594946324825287</v>
+        <v>0.2590957880020142</v>
       </c>
       <c r="C45" s="1">
         <v>118</v>
@@ -3023,7 +3023,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2462999969720841</v>
+        <v>0.2459214329719544</v>
       </c>
       <c r="C46" s="1">
         <v>112</v>
@@ -3049,7 +3049,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2155124992132187</v>
+        <v>0.2151812613010407</v>
       </c>
       <c r="C47" s="1">
         <v>98</v>
@@ -3075,7 +3075,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2155124992132187</v>
+        <v>0.2151812613010407</v>
       </c>
       <c r="C48" s="1">
         <v>98</v>
@@ -3101,7 +3101,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.1891232132911682</v>
+        <v>0.1888325363397598</v>
       </c>
       <c r="C49" s="1">
         <v>86</v>
@@ -3127,7 +3127,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.1407428532838821</v>
+        <v>0.1405265331268311</v>
       </c>
       <c r="C50" s="1">
         <v>64</v>
@@ -3153,7 +3153,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1055571436882019</v>
+        <v>0.1053948998451233</v>
       </c>
       <c r="C51" s="1">
         <v>48</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1055571436882019</v>
+        <v>0.1053948998451233</v>
       </c>
       <c r="C52" s="1">
         <v>48</v>
@@ -3205,7 +3205,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1055571436882019</v>
+        <v>0.1053948998451233</v>
       </c>
       <c r="C53" s="1">
         <v>48</v>
@@ -3231,7 +3231,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.09676071256399155</v>
+        <v>0.09661199152469635</v>
       </c>
       <c r="C54" s="1">
         <v>44</v>
@@ -3257,7 +3257,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.08796428889036179</v>
+        <v>0.08782908320426941</v>
       </c>
       <c r="C55" s="1">
         <v>40</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.08796428889036179</v>
+        <v>0.08782908320426941</v>
       </c>
       <c r="C56" s="1">
         <v>40</v>
@@ -3309,7 +3309,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.08356606960296631</v>
+        <v>0.08343762904405594</v>
       </c>
       <c r="C57" s="1">
         <v>38</v>
@@ -3335,7 +3335,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.07916785776615143</v>
+        <v>0.07904617488384247</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3361,7 +3361,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.07916785776615143</v>
+        <v>0.07904617488384247</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3387,7 +3387,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.07916785776615143</v>
+        <v>0.07904617488384247</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3413,7 +3413,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.07916785776615143</v>
+        <v>0.07904617488384247</v>
       </c>
       <c r="C61" s="1">
         <v>36</v>
@@ -3439,7 +3439,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.07037142664194107</v>
+        <v>0.07026326656341553</v>
       </c>
       <c r="C62" s="1">
         <v>32</v>
@@ -3465,7 +3465,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.06597321480512619</v>
+        <v>0.06587181240320206</v>
       </c>
       <c r="C63" s="1">
         <v>30</v>
@@ -3491,7 +3491,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.06597321480512619</v>
+        <v>0.06587181240320206</v>
       </c>
       <c r="C64" s="1">
         <v>30</v>
@@ -3517,7 +3517,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.05717678740620613</v>
+        <v>0.05708890408277512</v>
       </c>
       <c r="C65" s="1">
         <v>26</v>
@@ -3543,7 +3543,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.03078749962151051</v>
+        <v>0.03074017912149429</v>
       </c>
       <c r="C66" s="1">
         <v>14</v>
@@ -3569,7 +3569,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.01759285666048527</v>
+        <v>0.01756581664085388</v>
       </c>
       <c r="C67" s="1">
         <v>8</v>
@@ -3595,7 +3595,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.01759285666048527</v>
+        <v>0.01756581664085388</v>
       </c>
       <c r="C68" s="1">
         <v>8</v>
@@ -3621,7 +3621,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.008796428330242634</v>
+        <v>0.008782908320426941</v>
       </c>
       <c r="C69" s="1">
         <v>4</v>
@@ -3647,7 +3647,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.008796428330242634</v>
+        <v>0.008782908320426941</v>
       </c>
       <c r="C70" s="1">
         <v>4</v>
